--- a/src/ExcelsiorClosedXml.Tests/LinkTests.Test.verified.xlsx
+++ b/src/ExcelsiorClosedXml.Tests/LinkTests.Test.verified.xlsx
@@ -136,7 +136,7 @@
   <numFmts count="1">
     <numFmt numFmtId="0" formatCode=""/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <vertAlign val="baseline"/>
       <sz val="11"/>
@@ -157,6 +157,14 @@
       <vertAlign val="baseline"/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u val="single"/>
+      <vertAlign val="baseline"/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -188,7 +196,7 @@
       </diagonal>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <protection locked="1" hidden="0"/>
     </xf>
@@ -198,8 +206,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <protection locked="1" hidden="0"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <protection locked="1" hidden="0"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <protection locked="1" hidden="0"/>
@@ -213,6 +224,10 @@
       <protection locked="1" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="1" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <protection locked="1" hidden="0"/>
     </xf>
@@ -553,7 +568,7 @@
       <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F2" s="2" t="s">
@@ -565,6 +580,7 @@
   <hyperlinks>
     <hyperlink ref="B2" r:id="DeterministicId2"/>
     <hyperlink ref="C2" r:id="DeterministicId1"/>
+    <hyperlink ref="E2" r:id="DeterministicId3"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/src/ExcelsiorClosedXml.Tests/LinkTests.Test.verified.xlsx
+++ b/src/ExcelsiorClosedXml.Tests/LinkTests.Test.verified.xlsx
@@ -48,10 +48,9 @@
     <r>
       <rPr>
         <b/>
-        <u val="single"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
@@ -82,6 +81,16 @@
     <r>
       <rPr>
         <b/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">● </t>
+    </r>
+    <r>
+      <rPr>
         <u val="single"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
@@ -89,17 +98,6 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">● </t>
-    </r>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
       <t>GitHub (https://github.com)</t>
     </r>
   </si>
@@ -107,10 +105,9 @@
     <r>
       <rPr>
         <b/>
-        <u val="single"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>

--- a/src/ExcelsiorClosedXml.Tests/LinkTests.Test.verified.xlsx
+++ b/src/ExcelsiorClosedXml.Tests/LinkTests.Test.verified.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="DeterministicId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$2</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -573,7 +573,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F2"/>
+  <autoFilter ref="A1:C2"/>
   <hyperlinks>
     <hyperlink ref="B2" r:id="DeterministicId2"/>
     <hyperlink ref="C2" r:id="DeterministicId1"/>
